--- a/development/processed/airdata/correction_log_step_2.xlsx
+++ b/development/processed/airdata/correction_log_step_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Kuliah\Semester 8\IEEE - TIFS\droneNLP-data\processed\airdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Kuliah\Semester 8\IEEE - TIFS\dataset\development\processed\airdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B6240C-C879-4C73-A184-2AB2208319C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BE74A5-D176-45A8-A3EA-610C5804143A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{2C9B559C-DB3E-4A5F-A7EF-9A6DED2CF13B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C9B559C-DB3E-4A5F-A7EF-9A6DED2CF13B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="85">
   <si>
     <t>MessageID</t>
   </si>
@@ -282,6 +282,15 @@
   </si>
   <si>
     <t>Critically Low Voltage Warning. Land as soon as possible, otherwise the battery will be damaged</t>
+  </si>
+  <si>
+    <t>Remove the quotation marks</t>
+  </si>
+  <si>
+    <t>Aircraft close to Home Point. go home shifts to landing.</t>
+  </si>
+  <si>
+    <t>Cannot switch flight mode. Turn on Multiple Flight Modes to enable Atti and Sport Modes.</t>
   </si>
 </sst>
 </file>
@@ -660,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2728F41-E64C-41D0-B04E-388C9EF5B89E}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -699,83 +708,83 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
@@ -783,13 +792,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
@@ -797,55 +806,55 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
@@ -853,27 +862,27 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -881,69 +890,69 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s">
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>17</v>
+      <c r="C19" t="s">
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s">
         <v>5</v>
       </c>
-      <c r="C20" t="s">
-        <v>18</v>
+      <c r="C20" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
@@ -951,27 +960,27 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -979,13 +988,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
@@ -993,13 +1002,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -1007,13 +1016,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
@@ -1021,27 +1030,27 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>278</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
@@ -1049,27 +1058,27 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
@@ -1077,13 +1086,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
@@ -1091,41 +1100,41 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>316</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s">
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s">
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
         <v>6</v>
@@ -1133,83 +1142,83 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s">
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s">
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s">
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s">
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s">
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s">
         <v>6</v>
@@ -1217,13 +1226,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s">
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
         <v>6</v>
@@ -1231,13 +1240,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
         <v>6</v>
@@ -1245,13 +1254,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s">
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
         <v>6</v>
@@ -1259,41 +1268,41 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s">
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s">
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s">
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D45" t="s">
         <v>8</v>
@@ -1301,13 +1310,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B46" t="s">
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
         <v>8</v>
@@ -1315,13 +1324,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s">
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s">
         <v>8</v>
@@ -1329,13 +1338,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B48" t="s">
         <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D48" t="s">
         <v>8</v>
@@ -1343,13 +1352,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s">
         <v>5</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D49" t="s">
         <v>8</v>
@@ -1357,13 +1366,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B50" t="s">
         <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
@@ -1371,13 +1380,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s">
         <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D51" t="s">
         <v>8</v>
@@ -1385,27 +1394,27 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s">
         <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s">
         <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D53" t="s">
         <v>8</v>
@@ -1413,55 +1422,55 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="B55" t="s">
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D55" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>407</v>
+        <v>371</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C56" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D56" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s">
         <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D57" t="s">
         <v>54</v>
@@ -1469,69 +1478,69 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s">
         <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D58" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s">
         <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D59" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>485</v>
+        <v>420</v>
       </c>
       <c r="B60" t="s">
         <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D60" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B61" t="s">
         <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D61" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D62" t="s">
         <v>58</v>
@@ -1539,43 +1548,71 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s">
         <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D63" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s">
         <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65">
+        <v>493</v>
+      </c>
+      <c r="B65" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" t="s">
+        <v>62</v>
+      </c>
+      <c r="D65" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>494</v>
+      </c>
+      <c r="B66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
         <v>495</v>
       </c>
-      <c r="B65" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="B67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" t="s">
         <v>64</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D67" t="s">
         <v>54</v>
       </c>
     </row>
